--- a/public/templates/DentalIntra_Test_Data_Template_WithTimer.xlsx
+++ b/public/templates/DentalIntra_Test_Data_Template_WithTimer.xlsx
@@ -397,308 +397,1150 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N41"/>
+  <dimension ref="A1:N47"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>TEST: ACCURACY OF OPERATING POTENTIAL</v>
       </c>
+      <c r="B1" t="str">
+        <v/>
+      </c>
+      <c r="C1" t="str">
+        <v/>
+      </c>
+      <c r="D1" t="str">
+        <v/>
+      </c>
+      <c r="E1" t="str">
+        <v/>
+      </c>
+      <c r="F1" t="str">
+        <v/>
+      </c>
+      <c r="G1" t="str">
+        <v/>
+      </c>
+      <c r="H1" t="str">
+        <v/>
+      </c>
+      <c r="I1" t="str">
+        <v/>
+      </c>
+      <c r="J1" t="str">
+        <v/>
+      </c>
+      <c r="K1" t="str">
+        <v/>
+      </c>
+      <c r="L1" t="str">
+        <v/>
+      </c>
+      <c r="M1" t="str">
+        <v/>
+      </c>
+      <c r="N1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Applied kVp</v>
+        <v>Tolerance Sign</v>
       </c>
       <c r="B2" t="str">
-        <v>mA 1</v>
+        <v>±</v>
       </c>
       <c r="C2" t="str">
-        <v>mA 2</v>
+        <v/>
+      </c>
+      <c r="D2" t="str">
+        <v/>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2" t="str">
+        <v/>
+      </c>
+      <c r="I2" t="str">
+        <v/>
+      </c>
+      <c r="J2" t="str">
+        <v/>
+      </c>
+      <c r="K2" t="str">
+        <v/>
+      </c>
+      <c r="L2" t="str">
+        <v/>
+      </c>
+      <c r="M2" t="str">
+        <v/>
+      </c>
+      <c r="N2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>60</v>
+        <v>Tolerance Value (kVp)</v>
       </c>
       <c r="B3" t="str">
-        <v>60.1</v>
+        <v>5</v>
       </c>
       <c r="C3" t="str">
-        <v>60.2</v>
+        <v/>
+      </c>
+      <c r="D3" t="str">
+        <v/>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v/>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v/>
+      </c>
+      <c r="M3" t="str">
+        <v/>
+      </c>
+      <c r="N3" t="str">
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>80</v>
+        <v>Applied kVp</v>
       </c>
       <c r="B4" t="str">
-        <v>80.1</v>
+        <v>mA 1</v>
       </c>
       <c r="C4" t="str">
-        <v>80.2</v>
+        <v>mA 2</v>
+      </c>
+      <c r="D4" t="str">
+        <v/>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v/>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v/>
+      </c>
+      <c r="M4" t="str">
+        <v/>
+      </c>
+      <c r="N4" t="str">
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="B5" t="str">
-        <v>100.1</v>
+        <v>60.1</v>
       </c>
       <c r="C5" t="str">
-        <v>100.2</v>
+        <v>60.2</v>
+      </c>
+      <c r="D5" t="str">
+        <v/>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v/>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v/>
+      </c>
+      <c r="M5" t="str">
+        <v/>
+      </c>
+      <c r="N5" t="str">
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="B6" t="str">
-        <v>120.1</v>
+        <v>80.1</v>
       </c>
       <c r="C6" t="str">
-        <v>120.2</v>
+        <v>80.2</v>
+      </c>
+      <c r="D6" t="str">
+        <v/>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v/>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v/>
+      </c>
+      <c r="M6" t="str">
+        <v/>
+      </c>
+      <c r="N6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>100</v>
+      </c>
+      <c r="B7" t="str">
+        <v>100.1</v>
+      </c>
+      <c r="C7" t="str">
+        <v>100.2</v>
+      </c>
+      <c r="D7" t="str">
+        <v/>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v/>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v/>
+      </c>
+      <c r="M7" t="str">
+        <v/>
+      </c>
+      <c r="N7" t="str">
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>TEST: TOTAL FILTRATION</v>
+        <v>120</v>
+      </c>
+      <c r="B8" t="str">
+        <v>120.1</v>
+      </c>
+      <c r="C8" t="str">
+        <v>120.2</v>
+      </c>
+      <c r="D8" t="str">
+        <v/>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v/>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v/>
+      </c>
+      <c r="M8" t="str">
+        <v/>
+      </c>
+      <c r="N8" t="str">
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Total Filtration Measured (mm Al)</v>
+        <v/>
       </c>
       <c r="B9" t="str">
-        <v>2.1</v>
+        <v/>
+      </c>
+      <c r="C9" t="str">
+        <v/>
+      </c>
+      <c r="D9" t="str">
+        <v/>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v/>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v/>
+      </c>
+      <c r="M9" t="str">
+        <v/>
+      </c>
+      <c r="N9" t="str">
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Total Filtration Required (mm Al)</v>
+        <v>TEST: TOTAL FILTRATION</v>
       </c>
       <c r="B10" t="str">
-        <v>2.0</v>
+        <v/>
+      </c>
+      <c r="C10" t="str">
+        <v/>
+      </c>
+      <c r="D10" t="str">
+        <v/>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v/>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v/>
+      </c>
+      <c r="M10" t="str">
+        <v/>
+      </c>
+      <c r="N10" t="str">
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Total Filtration At kVp</v>
+        <v>Total Filtration Measured (mm Al)</v>
       </c>
       <c r="B11" t="str">
-        <v>80</v>
+        <v>2.1</v>
+      </c>
+      <c r="C11" t="str">
+        <v/>
+      </c>
+      <c r="D11" t="str">
+        <v/>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v/>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v/>
+      </c>
+      <c r="M11" t="str">
+        <v/>
+      </c>
+      <c r="N11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Total Filtration Required (mm Al)</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2.0</v>
+      </c>
+      <c r="C12" t="str">
+        <v/>
+      </c>
+      <c r="D12" t="str">
+        <v/>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v/>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v/>
+      </c>
+      <c r="M12" t="str">
+        <v/>
+      </c>
+      <c r="N12" t="str">
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>TEST: ACCURACY OF IRRADIATION TIME</v>
+        <v>Total Filtration At kVp</v>
+      </c>
+      <c r="B13" t="str">
+        <v>80</v>
+      </c>
+      <c r="C13" t="str">
+        <v/>
+      </c>
+      <c r="D13" t="str">
+        <v/>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v/>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v/>
+      </c>
+      <c r="M13" t="str">
+        <v/>
+      </c>
+      <c r="N13" t="str">
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>FCD</v>
+        <v/>
       </c>
       <c r="B14" t="str">
-        <v>kV</v>
+        <v/>
       </c>
       <c r="C14" t="str">
-        <v>mA</v>
+        <v/>
       </c>
       <c r="D14" t="str">
-        <v>Set Time (mSec)</v>
+        <v/>
       </c>
       <c r="E14" t="str">
-        <v>mA Station 1 Time</v>
+        <v/>
       </c>
       <c r="F14" t="str">
-        <v>mA Station 2 Time</v>
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v/>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v/>
+      </c>
+      <c r="M14" t="str">
+        <v/>
+      </c>
+      <c r="N14" t="str">
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>100</v>
+        <v>TEST: ACCURACY OF IRRADIATION TIME</v>
       </c>
       <c r="B15" t="str">
-        <v>80</v>
+        <v/>
       </c>
       <c r="C15" t="str">
-        <v>100</v>
+        <v/>
       </c>
       <c r="D15" t="str">
-        <v>100</v>
+        <v/>
       </c>
       <c r="E15" t="str">
-        <v>101</v>
+        <v/>
       </c>
       <c r="F15" t="str">
-        <v>99</v>
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v/>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v/>
+      </c>
+      <c r="M15" t="str">
+        <v/>
+      </c>
+      <c r="N15" t="str">
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
+        <v>FCD</v>
+      </c>
+      <c r="B16" t="str">
+        <v>kV</v>
+      </c>
+      <c r="C16" t="str">
+        <v>mA</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Set Time (mSec)</v>
+      </c>
+      <c r="E16" t="str">
+        <v>mA Station 1 Time</v>
+      </c>
+      <c r="F16" t="str">
+        <v>mA Station 2 Time</v>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v/>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
+        <v/>
+      </c>
+      <c r="M16" t="str">
+        <v/>
+      </c>
+      <c r="N16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
         <v>100</v>
       </c>
-      <c r="B16" t="str">
+      <c r="B17" t="str">
         <v>80</v>
       </c>
-      <c r="C16" t="str">
+      <c r="C17" t="str">
         <v>100</v>
       </c>
-      <c r="D16" t="str">
-        <v>200</v>
-      </c>
-      <c r="E16" t="str">
-        <v>201</v>
-      </c>
-      <c r="F16" t="str">
-        <v>199</v>
+      <c r="D17" t="str">
+        <v>100</v>
+      </c>
+      <c r="E17" t="str">
+        <v>101</v>
+      </c>
+      <c r="F17" t="str">
+        <v>99</v>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v/>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <v/>
+      </c>
+      <c r="L17" t="str">
+        <v/>
+      </c>
+      <c r="M17" t="str">
+        <v/>
+      </c>
+      <c r="N17" t="str">
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>TEST: LINEARITY OF TIME</v>
+        <v>100</v>
+      </c>
+      <c r="B18" t="str">
+        <v>80</v>
+      </c>
+      <c r="C18" t="str">
+        <v>100</v>
+      </c>
+      <c r="D18" t="str">
+        <v>200</v>
+      </c>
+      <c r="E18" t="str">
+        <v>201</v>
+      </c>
+      <c r="F18" t="str">
+        <v>199</v>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v/>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
+        <v/>
+      </c>
+      <c r="L18" t="str">
+        <v/>
+      </c>
+      <c r="M18" t="str">
+        <v/>
+      </c>
+      <c r="N18" t="str">
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>FCD</v>
+        <v/>
       </c>
       <c r="B19" t="str">
-        <v>kV</v>
+        <v/>
       </c>
       <c r="C19" t="str">
-        <v>mA</v>
+        <v/>
       </c>
       <c r="D19" t="str">
-        <v>Time Station (sec)</v>
+        <v/>
       </c>
       <c r="E19" t="str">
-        <v>Measured mR 1</v>
+        <v/>
       </c>
       <c r="F19" t="str">
-        <v>Measured mR 2</v>
+        <v/>
       </c>
       <c r="G19" t="str">
-        <v>Measured mR 3</v>
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
+        <v/>
+      </c>
+      <c r="J19" t="str">
+        <v/>
+      </c>
+      <c r="K19" t="str">
+        <v/>
+      </c>
+      <c r="L19" t="str">
+        <v/>
+      </c>
+      <c r="M19" t="str">
+        <v/>
+      </c>
+      <c r="N19" t="str">
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>100</v>
+        <v>TEST: LINEARITY OF TIME</v>
       </c>
       <c r="B20" t="str">
-        <v>80</v>
+        <v/>
       </c>
       <c r="C20" t="str">
-        <v>100</v>
+        <v/>
       </c>
       <c r="D20" t="str">
-        <v>0.1</v>
+        <v/>
       </c>
       <c r="E20" t="str">
-        <v>10.1</v>
+        <v/>
       </c>
       <c r="F20" t="str">
-        <v>10.2</v>
+        <v/>
       </c>
       <c r="G20" t="str">
-        <v>10.1</v>
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
+        <v/>
+      </c>
+      <c r="J20" t="str">
+        <v/>
+      </c>
+      <c r="K20" t="str">
+        <v/>
+      </c>
+      <c r="L20" t="str">
+        <v/>
+      </c>
+      <c r="M20" t="str">
+        <v/>
+      </c>
+      <c r="N20" t="str">
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
+        <v>FCD</v>
+      </c>
+      <c r="B21" t="str">
+        <v>kV</v>
+      </c>
+      <c r="C21" t="str">
+        <v>mA</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Time Station (sec)</v>
+      </c>
+      <c r="E21" t="str">
+        <v>Measured mR 1</v>
+      </c>
+      <c r="F21" t="str">
+        <v>Measured mR 2</v>
+      </c>
+      <c r="G21" t="str">
+        <v>Measured mR 3</v>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21" t="str">
+        <v/>
+      </c>
+      <c r="J21" t="str">
+        <v/>
+      </c>
+      <c r="K21" t="str">
+        <v/>
+      </c>
+      <c r="L21" t="str">
+        <v/>
+      </c>
+      <c r="M21" t="str">
+        <v/>
+      </c>
+      <c r="N21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
         <v>100</v>
       </c>
-      <c r="B21" t="str">
+      <c r="B22" t="str">
         <v>80</v>
       </c>
-      <c r="C21" t="str">
+      <c r="C22" t="str">
         <v>100</v>
       </c>
-      <c r="D21" t="str">
-        <v>0.2</v>
-      </c>
-      <c r="E21" t="str">
-        <v>20.1</v>
-      </c>
-      <c r="F21" t="str">
-        <v>20.2</v>
-      </c>
-      <c r="G21" t="str">
-        <v>20.1</v>
+      <c r="D22" t="str">
+        <v>0.1</v>
+      </c>
+      <c r="E22" t="str">
+        <v>10.1</v>
+      </c>
+      <c r="F22" t="str">
+        <v>10.2</v>
+      </c>
+      <c r="G22" t="str">
+        <v>10.1</v>
+      </c>
+      <c r="H22" t="str">
+        <v/>
+      </c>
+      <c r="I22" t="str">
+        <v/>
+      </c>
+      <c r="J22" t="str">
+        <v/>
+      </c>
+      <c r="K22" t="str">
+        <v/>
+      </c>
+      <c r="L22" t="str">
+        <v/>
+      </c>
+      <c r="M22" t="str">
+        <v/>
+      </c>
+      <c r="N22" t="str">
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>TEST: LINEARITY OF mA LOADING</v>
+        <v>100</v>
+      </c>
+      <c r="B23" t="str">
+        <v>80</v>
+      </c>
+      <c r="C23" t="str">
+        <v>100</v>
+      </c>
+      <c r="D23" t="str">
+        <v>0.2</v>
+      </c>
+      <c r="E23" t="str">
+        <v>20.1</v>
+      </c>
+      <c r="F23" t="str">
+        <v>20.2</v>
+      </c>
+      <c r="G23" t="str">
+        <v>20.1</v>
+      </c>
+      <c r="H23" t="str">
+        <v/>
+      </c>
+      <c r="I23" t="str">
+        <v/>
+      </c>
+      <c r="J23" t="str">
+        <v/>
+      </c>
+      <c r="K23" t="str">
+        <v/>
+      </c>
+      <c r="L23" t="str">
+        <v/>
+      </c>
+      <c r="M23" t="str">
+        <v/>
+      </c>
+      <c r="N23" t="str">
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>FCD</v>
+        <v/>
       </c>
       <c r="B24" t="str">
-        <v>kV</v>
+        <v/>
       </c>
       <c r="C24" t="str">
-        <v>Time</v>
+        <v/>
       </c>
       <c r="D24" t="str">
-        <v>mA Station</v>
+        <v/>
       </c>
       <c r="E24" t="str">
-        <v>Measured mR 1</v>
+        <v/>
       </c>
       <c r="F24" t="str">
-        <v>Measured mR 2</v>
+        <v/>
       </c>
       <c r="G24" t="str">
-        <v>Measured mR 3</v>
+        <v/>
+      </c>
+      <c r="H24" t="str">
+        <v/>
+      </c>
+      <c r="I24" t="str">
+        <v/>
+      </c>
+      <c r="J24" t="str">
+        <v/>
+      </c>
+      <c r="K24" t="str">
+        <v/>
+      </c>
+      <c r="L24" t="str">
+        <v/>
+      </c>
+      <c r="M24" t="str">
+        <v/>
+      </c>
+      <c r="N24" t="str">
+        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>100</v>
+        <v>TEST: LINEARITY OF mA LOADING</v>
       </c>
       <c r="B25" t="str">
-        <v>80</v>
+        <v/>
       </c>
       <c r="C25" t="str">
-        <v>0.5</v>
+        <v/>
       </c>
       <c r="D25" t="str">
-        <v>50</v>
+        <v/>
       </c>
       <c r="E25" t="str">
-        <v>5.1</v>
+        <v/>
       </c>
       <c r="F25" t="str">
-        <v>5.2</v>
+        <v/>
       </c>
       <c r="G25" t="str">
-        <v>5.1</v>
+        <v/>
+      </c>
+      <c r="H25" t="str">
+        <v/>
+      </c>
+      <c r="I25" t="str">
+        <v/>
+      </c>
+      <c r="J25" t="str">
+        <v/>
+      </c>
+      <c r="K25" t="str">
+        <v/>
+      </c>
+      <c r="L25" t="str">
+        <v/>
+      </c>
+      <c r="M25" t="str">
+        <v/>
+      </c>
+      <c r="N25" t="str">
+        <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>100</v>
+        <v>FCD</v>
       </c>
       <c r="B26" t="str">
-        <v>80</v>
+        <v>kV</v>
       </c>
       <c r="C26" t="str">
-        <v>0.5</v>
+        <v>Time</v>
       </c>
       <c r="D26" t="str">
-        <v>100</v>
+        <v>mA Station</v>
       </c>
       <c r="E26" t="str">
-        <v>10.1</v>
+        <v>Measured mR 1</v>
       </c>
       <c r="F26" t="str">
-        <v>10.2</v>
+        <v>Measured mR 2</v>
       </c>
       <c r="G26" t="str">
-        <v>10.1</v>
+        <v>Measured mR 3</v>
+      </c>
+      <c r="H26" t="str">
+        <v/>
+      </c>
+      <c r="I26" t="str">
+        <v/>
+      </c>
+      <c r="J26" t="str">
+        <v/>
+      </c>
+      <c r="K26" t="str">
+        <v/>
+      </c>
+      <c r="L26" t="str">
+        <v/>
+      </c>
+      <c r="M26" t="str">
+        <v/>
+      </c>
+      <c r="N26" t="str">
+        <v/>
       </c>
     </row>
     <row r="27">
@@ -712,16 +1554,37 @@
         <v>0.5</v>
       </c>
       <c r="D27" t="str">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="E27" t="str">
-        <v>20.1</v>
+        <v>5.1</v>
       </c>
       <c r="F27" t="str">
-        <v>20.2</v>
+        <v>5.2</v>
       </c>
       <c r="G27" t="str">
-        <v>20.1</v>
+        <v>5.1</v>
+      </c>
+      <c r="H27" t="str">
+        <v/>
+      </c>
+      <c r="I27" t="str">
+        <v/>
+      </c>
+      <c r="J27" t="str">
+        <v/>
+      </c>
+      <c r="K27" t="str">
+        <v/>
+      </c>
+      <c r="L27" t="str">
+        <v/>
+      </c>
+      <c r="M27" t="str">
+        <v/>
+      </c>
+      <c r="N27" t="str">
+        <v/>
       </c>
     </row>
     <row r="28">
@@ -735,224 +1598,806 @@
         <v>0.5</v>
       </c>
       <c r="D28" t="str">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="E28" t="str">
-        <v>30.1</v>
+        <v>10.1</v>
       </c>
       <c r="F28" t="str">
-        <v>30.2</v>
+        <v>10.2</v>
       </c>
       <c r="G28" t="str">
-        <v>30.1</v>
+        <v>10.1</v>
+      </c>
+      <c r="H28" t="str">
+        <v/>
+      </c>
+      <c r="I28" t="str">
+        <v/>
+      </c>
+      <c r="J28" t="str">
+        <v/>
+      </c>
+      <c r="K28" t="str">
+        <v/>
+      </c>
+      <c r="L28" t="str">
+        <v/>
+      </c>
+      <c r="M28" t="str">
+        <v/>
+      </c>
+      <c r="N28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>100</v>
+      </c>
+      <c r="B29" t="str">
+        <v>80</v>
+      </c>
+      <c r="C29" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="D29" t="str">
+        <v>200</v>
+      </c>
+      <c r="E29" t="str">
+        <v>20.1</v>
+      </c>
+      <c r="F29" t="str">
+        <v>20.2</v>
+      </c>
+      <c r="G29" t="str">
+        <v>20.1</v>
+      </c>
+      <c r="H29" t="str">
+        <v/>
+      </c>
+      <c r="I29" t="str">
+        <v/>
+      </c>
+      <c r="J29" t="str">
+        <v/>
+      </c>
+      <c r="K29" t="str">
+        <v/>
+      </c>
+      <c r="L29" t="str">
+        <v/>
+      </c>
+      <c r="M29" t="str">
+        <v/>
+      </c>
+      <c r="N29" t="str">
+        <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>TEST: CONSISTENCY OF RADIATION OUTPUT</v>
+        <v>100</v>
+      </c>
+      <c r="B30" t="str">
+        <v>80</v>
+      </c>
+      <c r="C30" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="D30" t="str">
+        <v>300</v>
+      </c>
+      <c r="E30" t="str">
+        <v>30.1</v>
+      </c>
+      <c r="F30" t="str">
+        <v>30.2</v>
+      </c>
+      <c r="G30" t="str">
+        <v>30.1</v>
+      </c>
+      <c r="H30" t="str">
+        <v/>
+      </c>
+      <c r="I30" t="str">
+        <v/>
+      </c>
+      <c r="J30" t="str">
+        <v/>
+      </c>
+      <c r="K30" t="str">
+        <v/>
+      </c>
+      <c r="L30" t="str">
+        <v/>
+      </c>
+      <c r="M30" t="str">
+        <v/>
+      </c>
+      <c r="N30" t="str">
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>FFD</v>
+        <v>Tolerance Operator</v>
       </c>
       <c r="B31" t="str">
-        <v>Test kV</v>
-      </c>
-      <c r="C31" t="str">
-        <v>Test mAs</v>
-      </c>
-      <c r="D31" t="str">
-        <v>Meas 1</v>
-      </c>
-      <c r="E31" t="str">
-        <v>Meas 2</v>
-      </c>
-      <c r="F31" t="str">
-        <v>Meas 3</v>
+        <v>&lt;=</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>40</v>
+        <v>Tolerance Value (CoL)</v>
       </c>
       <c r="B32" t="str">
-        <v>120</v>
-      </c>
-      <c r="C32" t="str">
-        <v>100</v>
-      </c>
-      <c r="D32" t="str">
-        <v>50.1</v>
-      </c>
-      <c r="E32" t="str">
-        <v>50.2</v>
-      </c>
-      <c r="F32" t="str">
-        <v>50.1</v>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v/>
+      </c>
+      <c r="B33" t="str">
+        <v/>
+      </c>
+      <c r="C33" t="str">
+        <v/>
+      </c>
+      <c r="D33" t="str">
+        <v/>
+      </c>
+      <c r="E33" t="str">
+        <v/>
+      </c>
+      <c r="F33" t="str">
+        <v/>
+      </c>
+      <c r="G33" t="str">
+        <v/>
+      </c>
+      <c r="H33" t="str">
+        <v/>
+      </c>
+      <c r="I33" t="str">
+        <v/>
+      </c>
+      <c r="J33" t="str">
+        <v/>
+      </c>
+      <c r="K33" t="str">
+        <v/>
+      </c>
+      <c r="L33" t="str">
+        <v/>
+      </c>
+      <c r="M33" t="str">
+        <v/>
+      </c>
+      <c r="N33" t="str">
+        <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>TEST: RADIATION LEAKAGE LEVEL</v>
+        <v>TEST: CONSISTENCY OF RADIATION OUTPUT</v>
+      </c>
+      <c r="B34" t="str">
+        <v/>
+      </c>
+      <c r="C34" t="str">
+        <v/>
+      </c>
+      <c r="D34" t="str">
+        <v/>
+      </c>
+      <c r="E34" t="str">
+        <v/>
+      </c>
+      <c r="F34" t="str">
+        <v/>
+      </c>
+      <c r="G34" t="str">
+        <v/>
+      </c>
+      <c r="H34" t="str">
+        <v/>
+      </c>
+      <c r="I34" t="str">
+        <v/>
+      </c>
+      <c r="J34" t="str">
+        <v/>
+      </c>
+      <c r="K34" t="str">
+        <v/>
+      </c>
+      <c r="L34" t="str">
+        <v/>
+      </c>
+      <c r="M34" t="str">
+        <v/>
+      </c>
+      <c r="N34" t="str">
+        <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Distance</v>
+        <v>Tolerance Operator</v>
       </c>
       <c r="B35" t="str">
-        <v>kV</v>
+        <v>&lt;=</v>
       </c>
       <c r="C35" t="str">
-        <v>mA</v>
+        <v/>
       </c>
       <c r="D35" t="str">
-        <v>Time</v>
+        <v/>
       </c>
       <c r="E35" t="str">
-        <v>Workload</v>
+        <v/>
       </c>
       <c r="F35" t="str">
-        <v>Tolerance Value</v>
+        <v/>
       </c>
       <c r="G35" t="str">
-        <v>Tolerance Operator</v>
+        <v/>
       </c>
       <c r="H35" t="str">
-        <v>Tolerance Time</v>
+        <v/>
       </c>
       <c r="I35" t="str">
-        <v>Location</v>
+        <v/>
       </c>
       <c r="J35" t="str">
-        <v>Front</v>
+        <v/>
       </c>
       <c r="K35" t="str">
-        <v>Back</v>
+        <v/>
       </c>
       <c r="L35" t="str">
-        <v>Left</v>
+        <v/>
       </c>
       <c r="M35" t="str">
-        <v>Right</v>
+        <v/>
       </c>
       <c r="N35" t="str">
-        <v>Top</v>
+        <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>100</v>
+        <v>Tolerance Value (CoV)</v>
       </c>
       <c r="B36" t="str">
-        <v>120</v>
+        <v>0.05</v>
       </c>
       <c r="C36" t="str">
-        <v>100</v>
+        <v/>
       </c>
       <c r="D36" t="str">
-        <v>1</v>
+        <v/>
       </c>
       <c r="E36" t="str">
-        <v>500</v>
+        <v/>
       </c>
       <c r="F36" t="str">
-        <v>1</v>
+        <v/>
       </c>
       <c r="G36" t="str">
-        <v>&lt;=</v>
+        <v/>
       </c>
       <c r="H36" t="str">
-        <v>1</v>
+        <v/>
       </c>
       <c r="I36" t="str">
-        <v>Tube</v>
+        <v/>
       </c>
       <c r="J36" t="str">
-        <v>0.01</v>
+        <v/>
       </c>
       <c r="K36" t="str">
-        <v>0.02</v>
+        <v/>
       </c>
       <c r="L36" t="str">
-        <v>0.01</v>
+        <v/>
       </c>
       <c r="M36" t="str">
-        <v>0.01</v>
+        <v/>
       </c>
       <c r="N36" t="str">
-        <v>0.02</v>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>FFD</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Test kV</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Test mAs</v>
+      </c>
+      <c r="D37" t="str">
+        <v>Meas 1</v>
+      </c>
+      <c r="E37" t="str">
+        <v>Meas 2</v>
+      </c>
+      <c r="F37" t="str">
+        <v>Meas 3</v>
+      </c>
+      <c r="G37" t="str">
+        <v/>
+      </c>
+      <c r="H37" t="str">
+        <v/>
+      </c>
+      <c r="I37" t="str">
+        <v/>
+      </c>
+      <c r="J37" t="str">
+        <v/>
+      </c>
+      <c r="K37" t="str">
+        <v/>
+      </c>
+      <c r="L37" t="str">
+        <v/>
+      </c>
+      <c r="M37" t="str">
+        <v/>
+      </c>
+      <c r="N37" t="str">
+        <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>TEST: RADIATION PROTECTION SURVEY REPORT</v>
+        <v>40</v>
+      </c>
+      <c r="B38" t="str">
+        <v>120</v>
+      </c>
+      <c r="C38" t="str">
+        <v>100</v>
+      </c>
+      <c r="D38" t="str">
+        <v>50.1</v>
+      </c>
+      <c r="E38" t="str">
+        <v>50.2</v>
+      </c>
+      <c r="F38" t="str">
+        <v>50.1</v>
+      </c>
+      <c r="G38" t="str">
+        <v/>
+      </c>
+      <c r="H38" t="str">
+        <v/>
+      </c>
+      <c r="I38" t="str">
+        <v/>
+      </c>
+      <c r="J38" t="str">
+        <v/>
+      </c>
+      <c r="K38" t="str">
+        <v/>
+      </c>
+      <c r="L38" t="str">
+        <v/>
+      </c>
+      <c r="M38" t="str">
+        <v/>
+      </c>
+      <c r="N38" t="str">
+        <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>kV</v>
+        <v/>
       </c>
       <c r="B39" t="str">
-        <v>mA</v>
+        <v/>
       </c>
       <c r="C39" t="str">
-        <v>Time</v>
+        <v/>
       </c>
       <c r="D39" t="str">
-        <v>Workload</v>
+        <v/>
       </c>
       <c r="E39" t="str">
-        <v>Location</v>
+        <v/>
       </c>
       <c r="F39" t="str">
-        <v>mR/hr</v>
+        <v/>
+      </c>
+      <c r="G39" t="str">
+        <v/>
+      </c>
+      <c r="H39" t="str">
+        <v/>
+      </c>
+      <c r="I39" t="str">
+        <v/>
+      </c>
+      <c r="J39" t="str">
+        <v/>
+      </c>
+      <c r="K39" t="str">
+        <v/>
+      </c>
+      <c r="L39" t="str">
+        <v/>
+      </c>
+      <c r="M39" t="str">
+        <v/>
+      </c>
+      <c r="N39" t="str">
+        <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>80</v>
+        <v>TEST: RADIATION LEAKAGE LEVEL</v>
       </c>
       <c r="B40" t="str">
-        <v>100</v>
+        <v/>
       </c>
       <c r="C40" t="str">
-        <v>0.5</v>
+        <v/>
       </c>
       <c r="D40" t="str">
-        <v>5000</v>
+        <v/>
       </c>
       <c r="E40" t="str">
-        <v>Control Console (Operator Position)</v>
+        <v/>
       </c>
       <c r="F40" t="str">
-        <v>0.02</v>
+        <v/>
+      </c>
+      <c r="G40" t="str">
+        <v/>
+      </c>
+      <c r="H40" t="str">
+        <v/>
+      </c>
+      <c r="I40" t="str">
+        <v/>
+      </c>
+      <c r="J40" t="str">
+        <v/>
+      </c>
+      <c r="K40" t="str">
+        <v/>
+      </c>
+      <c r="L40" t="str">
+        <v/>
+      </c>
+      <c r="M40" t="str">
+        <v/>
+      </c>
+      <c r="N40" t="str">
+        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
+        <v>Distance</v>
+      </c>
+      <c r="B41" t="str">
+        <v>kV</v>
+      </c>
+      <c r="C41" t="str">
+        <v>mA</v>
+      </c>
+      <c r="D41" t="str">
+        <v>Time</v>
+      </c>
+      <c r="E41" t="str">
+        <v>Workload</v>
+      </c>
+      <c r="F41" t="str">
+        <v>Tolerance Value</v>
+      </c>
+      <c r="G41" t="str">
+        <v>Tolerance Operator</v>
+      </c>
+      <c r="H41" t="str">
+        <v>Tolerance Time</v>
+      </c>
+      <c r="I41" t="str">
+        <v>Location</v>
+      </c>
+      <c r="J41" t="str">
+        <v>Front</v>
+      </c>
+      <c r="K41" t="str">
+        <v>Back</v>
+      </c>
+      <c r="L41" t="str">
+        <v>Left</v>
+      </c>
+      <c r="M41" t="str">
+        <v>Right</v>
+      </c>
+      <c r="N41" t="str">
+        <v>Top</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>100</v>
+      </c>
+      <c r="B42" t="str">
+        <v>120</v>
+      </c>
+      <c r="C42" t="str">
+        <v>100</v>
+      </c>
+      <c r="D42" t="str">
+        <v>1</v>
+      </c>
+      <c r="E42" t="str">
+        <v>500</v>
+      </c>
+      <c r="F42" t="str">
+        <v>1</v>
+      </c>
+      <c r="G42" t="str">
+        <v>&lt;=</v>
+      </c>
+      <c r="H42" t="str">
+        <v>1</v>
+      </c>
+      <c r="I42" t="str">
+        <v>Tube</v>
+      </c>
+      <c r="J42" t="str">
+        <v>0.01</v>
+      </c>
+      <c r="K42" t="str">
+        <v>0.02</v>
+      </c>
+      <c r="L42" t="str">
+        <v>0.01</v>
+      </c>
+      <c r="M42" t="str">
+        <v>0.01</v>
+      </c>
+      <c r="N42" t="str">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v/>
+      </c>
+      <c r="B43" t="str">
+        <v/>
+      </c>
+      <c r="C43" t="str">
+        <v/>
+      </c>
+      <c r="D43" t="str">
+        <v/>
+      </c>
+      <c r="E43" t="str">
+        <v/>
+      </c>
+      <c r="F43" t="str">
+        <v/>
+      </c>
+      <c r="G43" t="str">
+        <v/>
+      </c>
+      <c r="H43" t="str">
+        <v/>
+      </c>
+      <c r="I43" t="str">
+        <v/>
+      </c>
+      <c r="J43" t="str">
+        <v/>
+      </c>
+      <c r="K43" t="str">
+        <v/>
+      </c>
+      <c r="L43" t="str">
+        <v/>
+      </c>
+      <c r="M43" t="str">
+        <v/>
+      </c>
+      <c r="N43" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>TEST: RADIATION PROTECTION SURVEY REPORT</v>
+      </c>
+      <c r="B44" t="str">
+        <v/>
+      </c>
+      <c r="C44" t="str">
+        <v/>
+      </c>
+      <c r="D44" t="str">
+        <v/>
+      </c>
+      <c r="E44" t="str">
+        <v/>
+      </c>
+      <c r="F44" t="str">
+        <v/>
+      </c>
+      <c r="G44" t="str">
+        <v/>
+      </c>
+      <c r="H44" t="str">
+        <v/>
+      </c>
+      <c r="I44" t="str">
+        <v/>
+      </c>
+      <c r="J44" t="str">
+        <v/>
+      </c>
+      <c r="K44" t="str">
+        <v/>
+      </c>
+      <c r="L44" t="str">
+        <v/>
+      </c>
+      <c r="M44" t="str">
+        <v/>
+      </c>
+      <c r="N44" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>kV</v>
+      </c>
+      <c r="B45" t="str">
+        <v>mA</v>
+      </c>
+      <c r="C45" t="str">
+        <v>Time</v>
+      </c>
+      <c r="D45" t="str">
+        <v>Workload</v>
+      </c>
+      <c r="E45" t="str">
+        <v>Location</v>
+      </c>
+      <c r="F45" t="str">
+        <v>mR/hr</v>
+      </c>
+      <c r="G45" t="str">
+        <v/>
+      </c>
+      <c r="H45" t="str">
+        <v/>
+      </c>
+      <c r="I45" t="str">
+        <v/>
+      </c>
+      <c r="J45" t="str">
+        <v/>
+      </c>
+      <c r="K45" t="str">
+        <v/>
+      </c>
+      <c r="L45" t="str">
+        <v/>
+      </c>
+      <c r="M45" t="str">
+        <v/>
+      </c>
+      <c r="N45" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
         <v>80</v>
       </c>
-      <c r="B41" t="str">
+      <c r="B46" t="str">
         <v>100</v>
       </c>
-      <c r="C41" t="str">
+      <c r="C46" t="str">
         <v>0.5</v>
       </c>
-      <c r="D41" t="str">
+      <c r="D46" t="str">
         <v>5000</v>
       </c>
-      <c r="E41" t="str">
+      <c r="E46" t="str">
+        <v>Control Console (Operator Position)</v>
+      </c>
+      <c r="F46" t="str">
+        <v>0.02</v>
+      </c>
+      <c r="G46" t="str">
+        <v/>
+      </c>
+      <c r="H46" t="str">
+        <v/>
+      </c>
+      <c r="I46" t="str">
+        <v/>
+      </c>
+      <c r="J46" t="str">
+        <v/>
+      </c>
+      <c r="K46" t="str">
+        <v/>
+      </c>
+      <c r="L46" t="str">
+        <v/>
+      </c>
+      <c r="M46" t="str">
+        <v/>
+      </c>
+      <c r="N46" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>80</v>
+      </c>
+      <c r="B47" t="str">
+        <v>100</v>
+      </c>
+      <c r="C47" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="D47" t="str">
+        <v>5000</v>
+      </c>
+      <c r="E47" t="str">
         <v>Outside Patient Entrance Door</v>
       </c>
-      <c r="F41" t="str">
+      <c r="F47" t="str">
         <v>0.01</v>
+      </c>
+      <c r="G47" t="str">
+        <v/>
+      </c>
+      <c r="H47" t="str">
+        <v/>
+      </c>
+      <c r="I47" t="str">
+        <v/>
+      </c>
+      <c r="J47" t="str">
+        <v/>
+      </c>
+      <c r="K47" t="str">
+        <v/>
+      </c>
+      <c r="L47" t="str">
+        <v/>
+      </c>
+      <c r="M47" t="str">
+        <v/>
+      </c>
+      <c r="N47" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N41"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N47"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/templates/DentalIntra_Test_Data_Template_WithTimer.xlsx
+++ b/public/templates/DentalIntra_Test_Data_Template_WithTimer.xlsx
@@ -511,7 +511,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>FCD</v>
+        <v>FDD (cm)</v>
       </c>
       <c r="B16" t="str">
         <v>kV</v>
@@ -576,7 +576,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>FCD</v>
+        <v>FDD (cm)</v>
       </c>
       <c r="B21" t="str">
         <v>kV</v>
@@ -650,7 +650,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>FCD</v>
+        <v>FDD (cm)</v>
       </c>
       <c r="B26" t="str">
         <v>kV</v>
@@ -802,7 +802,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>FFD</v>
+        <v>FDD (cm)</v>
       </c>
       <c r="B37" t="str">
         <v>Test kV</v>
